--- a/reports/一级子公司B_利润表_2025-05.xlsx
+++ b/reports/一级子公司B_利润表_2025-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>49501937</v>
+        <v>65455485</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14687890</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>68031049</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>205038</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>959536</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>184324</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>862765</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>153586</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>718207</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>143480</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>669662</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>82138</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>382378</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>61749</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>286677</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>49501937</v>
+        <v>64625170</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13857575</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8284734</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>38278194</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1243415</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>5747682</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>621407</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>2876844</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4136718</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>19195652</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>412778</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>1920607</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>308810</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>1440628</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>513451</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>2400270</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>409992</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>1918854</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>49421750</v>
+        <v>49149296</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>229909748</v>
+        <v>230038778</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>80187</v>
+        <v>79532</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>400174</v>
+        <v>399901</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>922555</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4304466</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>616212</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2867630</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>45713441</v>
+        <v>58916741</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26004905</v>
+        <v>33340074</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>153695</v>
+        <v>7446802</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>717683</v>
+        <v>34424576</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>25851210</v>
+        <v>25893272</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>119854257</v>
+        <v>119634988</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1554263</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>7185626</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>497056</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2301773</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>310175</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1439809</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>371380</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1728618</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>277836</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1296542</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>184789</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>864033</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>153718</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>719487</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1229224</v>
+        <v>1228661</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5741149</v>
+        <v>5750162</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>41380</v>
+        <v>40962</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>191784</v>
+        <v>191469</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2567917</v>
+        <v>2563194</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>11967553</v>
+        <v>11955510</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>15462778</v>
+        <v>15409925</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>71865240</v>
+        <v>71686000</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2574623</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>11944632</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>448617</v>
+        <v>451047</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2248687</v>
+        <v>2244597</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401843</v>
+        <v>401756</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2001796</v>
+        <v>1996176</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>29831</v>
+        <v>30170</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>149833</v>
+        <v>149838</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>135806</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>674954</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>271784</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1258941</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>90318</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>450819</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67583</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>338296</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>112356</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>563898</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>384870</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1799923</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>59686</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>300444</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>44731</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>225117</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>74575</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>374803</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52271</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>262111</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37414</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>187092</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30006</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>149628</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22559</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>112234</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3788496</v>
+        <v>6649797</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-114888</v>
+        <v>4638893</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>155416</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>718767</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37689</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>187704</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>59694</v>
+        <v>60195</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>299700</v>
+        <v>300574</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3728802</v>
+        <v>6745018</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1789276</v>
+        <v>1797106</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>8989250</v>
+        <v>9022214</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1939526</v>
+        <v>4947912</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1939526</v>
+        <v>4947912</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1939526</v>
+        <v>4947912</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1939526</v>
+        <v>4947912</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1939526</v>
+        <v>4947912</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
